--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114389071</v>
+        <v>114389074</v>
       </c>
       <c r="B2" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524568</v>
+        <v>524520</v>
       </c>
       <c r="R2" t="n">
-        <v>6401373</v>
+        <v>6401425</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114388775</v>
+        <v>114389073</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524568</v>
+        <v>524520</v>
       </c>
       <c r="R3" t="n">
-        <v>6401367</v>
+        <v>6401425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114388842</v>
+        <v>114389069</v>
       </c>
       <c r="B4" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524565</v>
+        <v>524538</v>
       </c>
       <c r="R4" t="n">
-        <v>6401483</v>
+        <v>6401452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114389069</v>
+        <v>114388842</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524538</v>
+        <v>524565</v>
       </c>
       <c r="R5" t="n">
-        <v>6401452</v>
+        <v>6401483</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114388782</v>
+        <v>114388512</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,16 +1092,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bona, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524471</v>
+        <v>524575</v>
       </c>
       <c r="R6" t="n">
-        <v>6401348</v>
+        <v>6401453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1146,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114388617</v>
+        <v>114388615</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524516</v>
+        <v>524542</v>
       </c>
       <c r="R7" t="n">
-        <v>6401306</v>
+        <v>6401410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114388780</v>
+        <v>114388616</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524516</v>
+        <v>524579</v>
       </c>
       <c r="R8" t="n">
-        <v>6401320</v>
+        <v>6401401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114388777</v>
+        <v>114388617</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524535</v>
+        <v>524516</v>
       </c>
       <c r="R9" t="n">
-        <v>6401343</v>
+        <v>6401306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114389073</v>
+        <v>114388774</v>
       </c>
       <c r="B10" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524520</v>
+        <v>524576</v>
       </c>
       <c r="R10" t="n">
-        <v>6401425</v>
+        <v>6401369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114389070</v>
+        <v>114388775</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524536</v>
+        <v>524568</v>
       </c>
       <c r="R11" t="n">
-        <v>6401400</v>
+        <v>6401367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114388783</v>
+        <v>114388776</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524569</v>
+        <v>524587</v>
       </c>
       <c r="R12" t="n">
-        <v>6401369</v>
+        <v>6401376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114388512</v>
+        <v>114388777</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,20 +1776,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bona, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524575</v>
+        <v>524535</v>
       </c>
       <c r="R13" t="n">
-        <v>6401453</v>
+        <v>6401343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,7 +1826,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1904,15 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114388615</v>
+        <v>114388779</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524542</v>
+        <v>524556</v>
       </c>
       <c r="R14" t="n">
-        <v>6401410</v>
+        <v>6401400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,15 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114388774</v>
+        <v>114388780</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524576</v>
+        <v>524516</v>
       </c>
       <c r="R15" t="n">
-        <v>6401369</v>
+        <v>6401320</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,37 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114389074</v>
+        <v>114388781</v>
       </c>
       <c r="B16" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524520</v>
+        <v>524523</v>
       </c>
       <c r="R16" t="n">
-        <v>6401425</v>
+        <v>6401349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,15 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114388616</v>
+        <v>114388782</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524579</v>
+        <v>524471</v>
       </c>
       <c r="R17" t="n">
-        <v>6401401</v>
+        <v>6401348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,15 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114388781</v>
+        <v>114388783</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524523</v>
+        <v>524569</v>
       </c>
       <c r="R18" t="n">
-        <v>6401349</v>
+        <v>6401369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,15 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114388776</v>
+        <v>114389070</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524587</v>
+        <v>524536</v>
       </c>
       <c r="R19" t="n">
-        <v>6401376</v>
+        <v>6401400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,15 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114389072</v>
+        <v>114389071</v>
       </c>
       <c r="B20" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524550</v>
+        <v>524568</v>
       </c>
       <c r="R20" t="n">
-        <v>6401375</v>
+        <v>6401373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,37 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114388779</v>
+        <v>114389072</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524556</v>
+        <v>524550</v>
       </c>
       <c r="R21" t="n">
-        <v>6401400</v>
+        <v>6401375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,52 +1063,72 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114388512</v>
+        <v>135309665</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bona, Ög</t>
+          <t>Bergviks barrskog, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524575</v>
+        <v>524517</v>
       </c>
       <c r="R6" t="n">
-        <v>6401453</v>
+        <v>6401385</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1132,12 +1152,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög iväg mot öst när jag stötte på honom</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1146,26 +1181,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114388615</v>
+        <v>114388512</v>
       </c>
       <c r="B7" t="n">
         <v>99118</v>
@@ -1194,16 +1228,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bona, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524542</v>
+        <v>524575</v>
       </c>
       <c r="R7" t="n">
-        <v>6401410</v>
+        <v>6401453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1282,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1262,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114388616</v>
+        <v>114388615</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1297,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524579</v>
+        <v>524542</v>
       </c>
       <c r="R8" t="n">
-        <v>6401401</v>
+        <v>6401410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114388617</v>
+        <v>114388616</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1394,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524516</v>
+        <v>524579</v>
       </c>
       <c r="R9" t="n">
-        <v>6401306</v>
+        <v>6401401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114388774</v>
+        <v>114388617</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1491,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524576</v>
+        <v>524516</v>
       </c>
       <c r="R10" t="n">
-        <v>6401369</v>
+        <v>6401306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,7 +1592,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114388775</v>
+        <v>114388774</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1588,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524568</v>
+        <v>524576</v>
       </c>
       <c r="R11" t="n">
-        <v>6401367</v>
+        <v>6401369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1689,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114388776</v>
+        <v>114388775</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1685,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524587</v>
+        <v>524568</v>
       </c>
       <c r="R12" t="n">
-        <v>6401376</v>
+        <v>6401367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1786,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114388777</v>
+        <v>114388776</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1782,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524535</v>
+        <v>524587</v>
       </c>
       <c r="R13" t="n">
-        <v>6401343</v>
+        <v>6401376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,7 +1883,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114388779</v>
+        <v>114388777</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -1879,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524556</v>
+        <v>524535</v>
       </c>
       <c r="R14" t="n">
-        <v>6401400</v>
+        <v>6401343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1980,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114388780</v>
+        <v>114388779</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -1976,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524516</v>
+        <v>524556</v>
       </c>
       <c r="R15" t="n">
-        <v>6401320</v>
+        <v>6401400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,7 +2077,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114388781</v>
+        <v>114388780</v>
       </c>
       <c r="B16" t="n">
         <v>99118</v>
@@ -2073,10 +2112,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524523</v>
+        <v>524516</v>
       </c>
       <c r="R16" t="n">
-        <v>6401349</v>
+        <v>6401320</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,7 +2174,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114388782</v>
+        <v>114388781</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2170,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524471</v>
+        <v>524523</v>
       </c>
       <c r="R17" t="n">
-        <v>6401348</v>
+        <v>6401349</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,7 +2271,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114388783</v>
+        <v>114388782</v>
       </c>
       <c r="B18" t="n">
         <v>99118</v>
@@ -2267,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524569</v>
+        <v>524471</v>
       </c>
       <c r="R18" t="n">
-        <v>6401369</v>
+        <v>6401348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,7 +2368,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114389070</v>
+        <v>114388783</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2364,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524536</v>
+        <v>524569</v>
       </c>
       <c r="R19" t="n">
-        <v>6401400</v>
+        <v>6401369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2465,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114389071</v>
+        <v>114389070</v>
       </c>
       <c r="B20" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524568</v>
+        <v>524536</v>
       </c>
       <c r="R20" t="n">
-        <v>6401373</v>
+        <v>6401400</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,7 +2562,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114389072</v>
+        <v>114389071</v>
       </c>
       <c r="B21" t="n">
         <v>106244</v>
@@ -2558,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524550</v>
+        <v>524568</v>
       </c>
       <c r="R21" t="n">
-        <v>6401375</v>
+        <v>6401373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2617,6 +2656,229 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114389072</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bona, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>524550</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6401375</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135309595</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergviks barrskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>524517</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6401385</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114389074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114389073</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114389069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388842</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135309665</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388512</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388616</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388617</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388774</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388775</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388776</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388777</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388779</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388780</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388781</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388782</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114388783</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114389070</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2656,6 +2756,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114389071</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2753,6 +2858,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114389072</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2879,8 +2989,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135309595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>135309665</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>135309595</v>
       </c>
       <c r="B23" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -2869,7 +2869,7 @@
         <v>135309595</v>
       </c>
       <c r="B23" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,52 +1088,72 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114388512</v>
+        <v>135309665</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bona, Ög</t>
+          <t>Bergviks barrskog, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524575</v>
+        <v>524517</v>
       </c>
       <c r="R6" t="n">
-        <v>6401453</v>
+        <v>6401385</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1177,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög iväg mot öst när jag stötte på honom</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,31 +1206,30 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388512</t>
+          <t>https://artportalen.se/Sighting/135309665</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114388615</v>
+        <v>114388512</v>
       </c>
       <c r="B7" t="n">
         <v>99118</v>
@@ -1224,16 +1258,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bona, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524542</v>
+        <v>524575</v>
       </c>
       <c r="R7" t="n">
-        <v>6401410</v>
+        <v>6401453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,6 +1312,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,13 +1330,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388615</t>
+          <t>https://artportalen.se/Sighting/114388512</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114388616</v>
+        <v>114388615</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1332,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524579</v>
+        <v>524542</v>
       </c>
       <c r="R8" t="n">
-        <v>6401401</v>
+        <v>6401410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,13 +1432,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388616</t>
+          <t>https://artportalen.se/Sighting/114388615</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114388617</v>
+        <v>114388616</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1434,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524516</v>
+        <v>524579</v>
       </c>
       <c r="R9" t="n">
-        <v>6401306</v>
+        <v>6401401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,13 +1534,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388617</t>
+          <t>https://artportalen.se/Sighting/114388616</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114388774</v>
+        <v>114388617</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1536,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524576</v>
+        <v>524516</v>
       </c>
       <c r="R10" t="n">
-        <v>6401369</v>
+        <v>6401306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,13 +1636,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388774</t>
+          <t>https://artportalen.se/Sighting/114388617</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114388775</v>
+        <v>114388774</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1638,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524568</v>
+        <v>524576</v>
       </c>
       <c r="R11" t="n">
-        <v>6401367</v>
+        <v>6401369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,13 +1738,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388775</t>
+          <t>https://artportalen.se/Sighting/114388774</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114388776</v>
+        <v>114388775</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1740,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524587</v>
+        <v>524568</v>
       </c>
       <c r="R12" t="n">
-        <v>6401376</v>
+        <v>6401367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,13 +1840,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388776</t>
+          <t>https://artportalen.se/Sighting/114388775</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114388777</v>
+        <v>114388776</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1842,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524535</v>
+        <v>524587</v>
       </c>
       <c r="R13" t="n">
-        <v>6401343</v>
+        <v>6401376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,13 +1942,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388777</t>
+          <t>https://artportalen.se/Sighting/114388776</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114388779</v>
+        <v>114388777</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -1944,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524556</v>
+        <v>524535</v>
       </c>
       <c r="R14" t="n">
-        <v>6401400</v>
+        <v>6401343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,13 +2044,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388779</t>
+          <t>https://artportalen.se/Sighting/114388777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114388780</v>
+        <v>114388779</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -2046,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524516</v>
+        <v>524556</v>
       </c>
       <c r="R15" t="n">
-        <v>6401320</v>
+        <v>6401400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,13 +2146,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388780</t>
+          <t>https://artportalen.se/Sighting/114388779</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114388781</v>
+        <v>114388780</v>
       </c>
       <c r="B16" t="n">
         <v>99118</v>
@@ -2148,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524523</v>
+        <v>524516</v>
       </c>
       <c r="R16" t="n">
-        <v>6401349</v>
+        <v>6401320</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,13 +2248,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388781</t>
+          <t>https://artportalen.se/Sighting/114388780</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114388782</v>
+        <v>114388781</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2250,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524471</v>
+        <v>524523</v>
       </c>
       <c r="R17" t="n">
-        <v>6401348</v>
+        <v>6401349</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,13 +2350,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388782</t>
+          <t>https://artportalen.se/Sighting/114388781</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114388783</v>
+        <v>114388782</v>
       </c>
       <c r="B18" t="n">
         <v>99118</v>
@@ -2352,10 +2391,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524569</v>
+        <v>524471</v>
       </c>
       <c r="R18" t="n">
-        <v>6401369</v>
+        <v>6401348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,13 +2452,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114388783</t>
+          <t>https://artportalen.se/Sighting/114388782</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114389070</v>
+        <v>114388783</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2454,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524536</v>
+        <v>524569</v>
       </c>
       <c r="R19" t="n">
-        <v>6401400</v>
+        <v>6401369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,38 +2554,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114389070</t>
+          <t>https://artportalen.se/Sighting/114388783</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114389071</v>
+        <v>114389070</v>
       </c>
       <c r="B20" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524568</v>
+        <v>524536</v>
       </c>
       <c r="R20" t="n">
-        <v>6401373</v>
+        <v>6401400</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,13 +2656,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114389071</t>
+          <t>https://artportalen.se/Sighting/114389070</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114389072</v>
+        <v>114389071</v>
       </c>
       <c r="B21" t="n">
         <v>106244</v>
@@ -2658,10 +2697,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524550</v>
+        <v>524568</v>
       </c>
       <c r="R21" t="n">
-        <v>6401375</v>
+        <v>6401373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,7 +2758,240 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/114389071</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114389072</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bona, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>524550</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6401375</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/114389072</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135309595</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106411</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergviks barrskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>524517</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6401385</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135309595</t>
         </is>
       </c>
     </row>
@@ -2745,6 +3017,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36721-2023 artfynd.xlsx
+++ b/artfynd/A 36721-2023 artfynd.xlsx
@@ -2869,7 +2869,7 @@
         <v>135309595</v>
       </c>
       <c r="B23" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
